--- a/samples/Chart_of_Accounts_IN_sample.xlsx
+++ b/samples/Chart_of_Accounts_IN_sample.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D42"/>
   <cols>
     <col min="1" max="1" width="52.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -575,10 +575,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Advance to Suppliers</v>
+        <v>Due from Aistra Labs AI Software LLC (UAE)</v>
       </c>
       <c r="B13" t="str">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="C13" t="str">
         <v>Other Current Asset</v>
@@ -589,13 +589,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Computers and Equipment</v>
+        <v>Due from Unconstrained INC</v>
       </c>
       <c r="B14" t="str">
-        <v>1500</v>
+        <v>1453</v>
       </c>
       <c r="C14" t="str">
-        <v>Fixed Asset</v>
+        <v>Other Current Asset</v>
       </c>
       <c r="D14" t="str">
         <v/>
@@ -603,13 +603,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Accumulated Depreciation - Computers and Equipment</v>
+        <v>Advance to Suppliers</v>
       </c>
       <c r="B15" t="str">
-        <v>1510</v>
+        <v>1455</v>
       </c>
       <c r="C15" t="str">
-        <v>Fixed Asset</v>
+        <v>Other Current Asset</v>
       </c>
       <c r="D15" t="str">
         <v/>
@@ -617,13 +617,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Deferred Tax Asset</v>
+        <v>Computers and Equipment</v>
       </c>
       <c r="B16" t="str">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="C16" t="str">
-        <v>Other Asset</v>
+        <v>Fixed Asset</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -631,13 +631,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Accounts Payable</v>
+        <v>Accumulated Depreciation - Computers and Equipment</v>
       </c>
       <c r="B17" t="str">
-        <v>2001</v>
+        <v>1510</v>
       </c>
       <c r="C17" t="str">
-        <v>Accounts Payable</v>
+        <v>Fixed Asset</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -645,13 +645,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Accrued Expenses</v>
+        <v>Deferred Tax Asset</v>
       </c>
       <c r="B18" t="str">
-        <v>2100</v>
+        <v>1600</v>
       </c>
       <c r="C18" t="str">
-        <v>Other Current Liability</v>
+        <v>Other Asset</v>
       </c>
       <c r="D18" t="str">
         <v/>
@@ -659,13 +659,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Income Tax Payable</v>
+        <v>Accounts Payable</v>
       </c>
       <c r="B19" t="str">
-        <v>2150</v>
+        <v>2001</v>
       </c>
       <c r="C19" t="str">
-        <v>Other Current Liability</v>
+        <v>Accounts Payable</v>
       </c>
       <c r="D19" t="str">
         <v/>
@@ -673,10 +673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Provision for Leave Encashment</v>
+        <v>Accrued Expenses</v>
       </c>
       <c r="B20" t="str">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="C20" t="str">
         <v>Other Current Liability</v>
@@ -687,13 +687,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Equity Share Capital</v>
+        <v>Income Tax Payable</v>
       </c>
       <c r="B21" t="str">
-        <v>3001</v>
+        <v>2150</v>
       </c>
       <c r="C21" t="str">
-        <v>Equity</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -701,13 +701,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Securities Premium</v>
+        <v>Provision for Leave Encashment</v>
       </c>
       <c r="B22" t="str">
-        <v>3100</v>
+        <v>2200</v>
       </c>
       <c r="C22" t="str">
-        <v>Equity</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -715,10 +715,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Retained Earnings</v>
+        <v>Equity Share Capital</v>
       </c>
       <c r="B23" t="str">
-        <v>3200</v>
+        <v>3001</v>
       </c>
       <c r="C23" t="str">
         <v>Equity</v>
@@ -729,13 +729,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Consulting Revenue</v>
+        <v>Securities Premium</v>
       </c>
       <c r="B24" t="str">
-        <v>4001</v>
+        <v>3100</v>
       </c>
       <c r="C24" t="str">
-        <v>Income</v>
+        <v>Equity</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -743,13 +743,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>IC Revenue - US</v>
+        <v>Retained Earnings</v>
       </c>
       <c r="B25" t="str">
-        <v>4100</v>
+        <v>3200</v>
       </c>
       <c r="C25" t="str">
-        <v>Income</v>
+        <v>Equity</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -757,10 +757,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>IC Revenue - UK</v>
+        <v>Consulting Revenue</v>
       </c>
       <c r="B26" t="str">
-        <v>4101</v>
+        <v>4001</v>
       </c>
       <c r="C26" t="str">
         <v>Income</v>
@@ -771,13 +771,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Interest Income</v>
+        <v>IC Revenue - US</v>
       </c>
       <c r="B27" t="str">
-        <v>4500</v>
+        <v>4100</v>
       </c>
       <c r="C27" t="str">
-        <v>Other Income</v>
+        <v>Income</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -785,13 +785,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Cost of Services</v>
+        <v>IC Revenue - UK</v>
       </c>
       <c r="B28" t="str">
-        <v>5001</v>
+        <v>4101</v>
       </c>
       <c r="C28" t="str">
-        <v>Cost Of Goods Sold</v>
+        <v>Income</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -799,13 +799,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Salaries and Wages</v>
+        <v>IC Revenue - UAE</v>
       </c>
       <c r="B29" t="str">
-        <v>6001</v>
+        <v>4102</v>
       </c>
       <c r="C29" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="D29" t="str">
         <v/>
@@ -813,13 +813,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Travel and Conveyance</v>
+        <v>IC Revenue - Unconstrained</v>
       </c>
       <c r="B30" t="str">
-        <v>6100</v>
+        <v>4103</v>
       </c>
       <c r="C30" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -827,13 +827,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Staff Welfare Expenses</v>
+        <v>Interest Income</v>
       </c>
       <c r="B31" t="str">
-        <v>6120</v>
+        <v>4500</v>
       </c>
       <c r="C31" t="str">
-        <v>Expense</v>
+        <v>Other Income</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -841,13 +841,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Professional Fees</v>
+        <v>Cost of Services</v>
       </c>
       <c r="B32" t="str">
-        <v>6200</v>
+        <v>5001</v>
       </c>
       <c r="C32" t="str">
-        <v>Expense</v>
+        <v>Cost Of Goods Sold</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -855,10 +855,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Software Subscriptions</v>
+        <v>Salaries and Wages</v>
       </c>
       <c r="B33" t="str">
-        <v>6300</v>
+        <v>6001</v>
       </c>
       <c r="C33" t="str">
         <v>Expense</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Rent</v>
+        <v>Travel and Conveyance</v>
       </c>
       <c r="B34" t="str">
-        <v>6400</v>
+        <v>6100</v>
       </c>
       <c r="C34" t="str">
         <v>Expense</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Depreciation</v>
+        <v>Staff Welfare Expenses</v>
       </c>
       <c r="B35" t="str">
-        <v>6500</v>
+        <v>6120</v>
       </c>
       <c r="C35" t="str">
         <v>Expense</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Income Tax Expense</v>
+        <v>Professional Fees</v>
       </c>
       <c r="B36" t="str">
-        <v>6900</v>
+        <v>6200</v>
       </c>
       <c r="C36" t="str">
         <v>Expense</v>
@@ -911,10 +911,10 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Office Supplies</v>
+        <v>Software Subscriptions</v>
       </c>
       <c r="B37" t="str">
-        <v>6150</v>
+        <v>6300</v>
       </c>
       <c r="C37" t="str">
         <v>Expense</v>
@@ -925,21 +925,77 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="B38" t="str">
+        <v>6400</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Depreciation</v>
+      </c>
+      <c r="B39" t="str">
+        <v>6500</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Income Tax Expense</v>
+      </c>
+      <c r="B40" t="str">
+        <v>6900</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="B41" t="str">
+        <v>6150</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
         <v>Fixed Deposit - HDFC</v>
       </c>
-      <c r="B38" t="str">
+      <c r="B42" t="str">
         <v>1060</v>
       </c>
-      <c r="C38" t="str">
+      <c r="C42" t="str">
         <v>Bank</v>
       </c>
-      <c r="D38" t="str">
+      <c r="D42" t="str">
         <v>HDFC Bank Current Account</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D42"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/Chart_of_Accounts_IN_sample.xlsx
+++ b/samples/Chart_of_Accounts_IN_sample.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D51"/>
   <cols>
     <col min="1" max="1" width="52.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -463,13 +463,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Prepaid Expenses</v>
+        <v>Security Deposit</v>
       </c>
       <c r="B5" t="str">
         <v>1200</v>
       </c>
       <c r="C5" t="str">
-        <v>Other Current Asset</v>
+        <v>Other Asset</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -491,13 +491,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Security Deposit</v>
+        <v>TDS Receivable</v>
       </c>
       <c r="B7" t="str">
-        <v>1300</v>
+        <v>1260</v>
       </c>
       <c r="C7" t="str">
-        <v>Other Asset</v>
+        <v>Other Current Asset</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -505,13 +505,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Investment - Aistra Labs AI Software LLC (UAE)</v>
+        <v>Prepaid Expenses</v>
       </c>
       <c r="B8" t="str">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="C8" t="str">
-        <v>Other Asset</v>
+        <v>Other Current Asset</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -519,10 +519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Investment - Aistra Labs UK Ltd</v>
+        <v>Investment - Aistra Labs AI Software LLC (UAE)</v>
       </c>
       <c r="B9" t="str">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C9" t="str">
         <v>Other Asset</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Investment - Unconstrained INC</v>
+        <v>Investment - Aistra Labs UK Ltd</v>
       </c>
       <c r="B10" t="str">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="C10" t="str">
         <v>Other Asset</v>
@@ -547,13 +547,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Due from Aistra Labs Inc (US)</v>
+        <v>Investment - Unconstrained INC</v>
       </c>
       <c r="B11" t="str">
-        <v>1450</v>
+        <v>1402</v>
       </c>
       <c r="C11" t="str">
-        <v>Other Current Asset</v>
+        <v>Other Asset</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -561,10 +561,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Due from Aistra Labs UK Ltd</v>
+        <v>Due from Aistra Labs Inc (US)</v>
       </c>
       <c r="B12" t="str">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="C12" t="str">
         <v>Other Current Asset</v>
@@ -575,10 +575,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Due from Aistra Labs AI Software LLC (UAE)</v>
+        <v>Due from Aistra Labs UK Ltd</v>
       </c>
       <c r="B13" t="str">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="C13" t="str">
         <v>Other Current Asset</v>
@@ -589,10 +589,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Due from Unconstrained INC</v>
+        <v>Due from Aistra Labs AI Software LLC (UAE)</v>
       </c>
       <c r="B14" t="str">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="C14" t="str">
         <v>Other Current Asset</v>
@@ -603,10 +603,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Advance to Suppliers</v>
+        <v>Due from Unconstrained INC</v>
       </c>
       <c r="B15" t="str">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="C15" t="str">
         <v>Other Current Asset</v>
@@ -617,13 +617,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Computers and Equipment</v>
+        <v>Advance to Suppliers</v>
       </c>
       <c r="B16" t="str">
-        <v>1500</v>
+        <v>1455</v>
       </c>
       <c r="C16" t="str">
-        <v>Fixed Asset</v>
+        <v>Other Current Asset</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -631,10 +631,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Accumulated Depreciation - Computers and Equipment</v>
+        <v>Computers and Equipment</v>
       </c>
       <c r="B17" t="str">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="C17" t="str">
         <v>Fixed Asset</v>
@@ -645,13 +645,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Deferred Tax Asset</v>
+        <v>Accumulated Depreciation - Computers and Equipment</v>
       </c>
       <c r="B18" t="str">
-        <v>1600</v>
+        <v>1510</v>
       </c>
       <c r="C18" t="str">
-        <v>Other Asset</v>
+        <v>Fixed Asset</v>
       </c>
       <c r="D18" t="str">
         <v/>
@@ -659,13 +659,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Accounts Payable</v>
+        <v>Furniture and Fixtures</v>
       </c>
       <c r="B19" t="str">
-        <v>2001</v>
+        <v>1520</v>
       </c>
       <c r="C19" t="str">
-        <v>Accounts Payable</v>
+        <v>Fixed Asset</v>
       </c>
       <c r="D19" t="str">
         <v/>
@@ -673,13 +673,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Accrued Expenses</v>
+        <v>Accumulated Depreciation - Furniture and Fixtures</v>
       </c>
       <c r="B20" t="str">
-        <v>2100</v>
+        <v>1530</v>
       </c>
       <c r="C20" t="str">
-        <v>Other Current Liability</v>
+        <v>Fixed Asset</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -687,13 +687,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Income Tax Payable</v>
+        <v>Deferred Tax Asset</v>
       </c>
       <c r="B21" t="str">
-        <v>2150</v>
+        <v>1600</v>
       </c>
       <c r="C21" t="str">
-        <v>Other Current Liability</v>
+        <v>Other Asset</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -701,13 +701,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Provision for Leave Encashment</v>
+        <v>Accounts Payable</v>
       </c>
       <c r="B22" t="str">
-        <v>2200</v>
+        <v>2001</v>
       </c>
       <c r="C22" t="str">
-        <v>Other Current Liability</v>
+        <v>Accounts Payable</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -715,13 +715,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Equity Share Capital</v>
+        <v>Accrued Expenses</v>
       </c>
       <c r="B23" t="str">
-        <v>3001</v>
+        <v>2100</v>
       </c>
       <c r="C23" t="str">
-        <v>Equity</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -729,13 +729,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Securities Premium</v>
+        <v>Income Tax Payable</v>
       </c>
       <c r="B24" t="str">
-        <v>3100</v>
+        <v>2150</v>
       </c>
       <c r="C24" t="str">
-        <v>Equity</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -743,13 +743,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Retained Earnings</v>
+        <v>Provision for Leave Encashment</v>
       </c>
       <c r="B25" t="str">
-        <v>3200</v>
+        <v>2200</v>
       </c>
       <c r="C25" t="str">
-        <v>Equity</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -757,13 +757,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Consulting Revenue</v>
+        <v>Provision for Gratuity</v>
       </c>
       <c r="B26" t="str">
-        <v>4001</v>
+        <v>2210</v>
       </c>
       <c r="C26" t="str">
-        <v>Income</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D26" t="str">
         <v/>
@@ -771,13 +771,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>IC Revenue - US</v>
+        <v>TDS Payable</v>
       </c>
       <c r="B27" t="str">
-        <v>4100</v>
+        <v>2300</v>
       </c>
       <c r="C27" t="str">
-        <v>Income</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -785,13 +785,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>IC Revenue - UK</v>
+        <v>Equity Share Capital</v>
       </c>
       <c r="B28" t="str">
-        <v>4101</v>
+        <v>3001</v>
       </c>
       <c r="C28" t="str">
-        <v>Income</v>
+        <v>Equity</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -799,13 +799,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>IC Revenue - UAE</v>
+        <v>Securities Premium</v>
       </c>
       <c r="B29" t="str">
-        <v>4102</v>
+        <v>3100</v>
       </c>
       <c r="C29" t="str">
-        <v>Income</v>
+        <v>Equity</v>
       </c>
       <c r="D29" t="str">
         <v/>
@@ -813,13 +813,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>IC Revenue - Unconstrained</v>
+        <v>Retained Earnings</v>
       </c>
       <c r="B30" t="str">
-        <v>4103</v>
+        <v>3200</v>
       </c>
       <c r="C30" t="str">
-        <v>Income</v>
+        <v>Equity</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -827,13 +827,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Interest Income</v>
+        <v>Consulting Revenue</v>
       </c>
       <c r="B31" t="str">
-        <v>4500</v>
+        <v>4001</v>
       </c>
       <c r="C31" t="str">
-        <v>Other Income</v>
+        <v>Income</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -841,13 +841,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Cost of Services</v>
+        <v>IC Revenue - US</v>
       </c>
       <c r="B32" t="str">
-        <v>5001</v>
+        <v>4100</v>
       </c>
       <c r="C32" t="str">
-        <v>Cost Of Goods Sold</v>
+        <v>Income</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -855,13 +855,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Salaries and Wages</v>
+        <v>IC Revenue - UK</v>
       </c>
       <c r="B33" t="str">
-        <v>6001</v>
+        <v>4101</v>
       </c>
       <c r="C33" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="D33" t="str">
         <v/>
@@ -869,13 +869,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Travel and Conveyance</v>
+        <v>IC Revenue - UAE</v>
       </c>
       <c r="B34" t="str">
-        <v>6100</v>
+        <v>4102</v>
       </c>
       <c r="C34" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="D34" t="str">
         <v/>
@@ -883,13 +883,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Staff Welfare Expenses</v>
+        <v>IC Revenue - Unconstrained</v>
       </c>
       <c r="B35" t="str">
-        <v>6120</v>
+        <v>4103</v>
       </c>
       <c r="C35" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -897,13 +897,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Professional Fees</v>
+        <v>Interest Income</v>
       </c>
       <c r="B36" t="str">
-        <v>6200</v>
+        <v>4500</v>
       </c>
       <c r="C36" t="str">
-        <v>Expense</v>
+        <v>Other Income</v>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -911,13 +911,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Software Subscriptions</v>
+        <v>Cost of Services</v>
       </c>
       <c r="B37" t="str">
-        <v>6300</v>
+        <v>5001</v>
       </c>
       <c r="C37" t="str">
-        <v>Expense</v>
+        <v>Cost Of Goods Sold</v>
       </c>
       <c r="D37" t="str">
         <v/>
@@ -925,10 +925,10 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Rent</v>
+        <v>Salaries and Wages</v>
       </c>
       <c r="B38" t="str">
-        <v>6400</v>
+        <v>6001</v>
       </c>
       <c r="C38" t="str">
         <v>Expense</v>
@@ -939,10 +939,10 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Depreciation</v>
+        <v>Contribution to Provident Fund</v>
       </c>
       <c r="B39" t="str">
-        <v>6500</v>
+        <v>6010</v>
       </c>
       <c r="C39" t="str">
         <v>Expense</v>
@@ -953,10 +953,10 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Income Tax Expense</v>
+        <v>Travel and Conveyance</v>
       </c>
       <c r="B40" t="str">
-        <v>6900</v>
+        <v>6100</v>
       </c>
       <c r="C40" t="str">
         <v>Expense</v>
@@ -967,10 +967,10 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Office Supplies</v>
+        <v>Staff Welfare Expenses</v>
       </c>
       <c r="B41" t="str">
-        <v>6150</v>
+        <v>6120</v>
       </c>
       <c r="C41" t="str">
         <v>Expense</v>
@@ -981,21 +981,147 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
+        <v>Professional Fees</v>
+      </c>
+      <c r="B42" t="str">
+        <v>6200</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Audit Fees</v>
+      </c>
+      <c r="B43" t="str">
+        <v>6210</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Software Subscriptions</v>
+      </c>
+      <c r="B44" t="str">
+        <v>6300</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Office Expenses</v>
+      </c>
+      <c r="B45" t="str">
+        <v>6400</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="B46" t="str">
+        <v>6410</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Depreciation</v>
+      </c>
+      <c r="B47" t="str">
+        <v>6500</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Income Tax Expense</v>
+      </c>
+      <c r="B48" t="str">
+        <v>6900</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Deferred Tax Expense</v>
+      </c>
+      <c r="B49" t="str">
+        <v>6910</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="B50" t="str">
+        <v>6150</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
         <v>Fixed Deposit - HDFC</v>
       </c>
-      <c r="B42" t="str">
+      <c r="B51" t="str">
         <v>1060</v>
       </c>
-      <c r="C42" t="str">
+      <c r="C51" t="str">
         <v>Bank</v>
       </c>
-      <c r="D42" t="str">
+      <c r="D51" t="str">
         <v>HDFC Bank Current Account</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/Chart_of_Accounts_IN_sample.xlsx
+++ b/samples/Chart_of_Accounts_IN_sample.xlsx
@@ -421,10 +421,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HDFC Bank Current Account</v>
+        <v>Operating Bank</v>
       </c>
       <c r="B2" t="str">
-        <v>1001</v>
+        <v>1010</v>
       </c>
       <c r="C2" t="str">
         <v>Bank</v>
@@ -438,7 +438,7 @@
         <v>Petty Cash</v>
       </c>
       <c r="B3" t="str">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C3" t="str">
         <v>Cash</v>
@@ -505,10 +505,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Prepaid Expenses</v>
+        <v>GST Input Credit</v>
       </c>
       <c r="B8" t="str">
-        <v>1300</v>
+        <v>1270</v>
       </c>
       <c r="C8" t="str">
         <v>Other Current Asset</v>
@@ -519,13 +519,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Investment - Aistra Labs AI Software LLC (UAE)</v>
+        <v>Prepaid Expenses</v>
       </c>
       <c r="B9" t="str">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="C9" t="str">
-        <v>Other Asset</v>
+        <v>Other Current Asset</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -533,10 +533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Investment - Aistra Labs UK Ltd</v>
+        <v>Investment - Aistra Labs AI Software LLC (UAE)</v>
       </c>
       <c r="B10" t="str">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C10" t="str">
         <v>Other Asset</v>
@@ -547,10 +547,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Investment - Unconstrained INC</v>
+        <v>Investment - Aistra Labs UK Ltd</v>
       </c>
       <c r="B11" t="str">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="C11" t="str">
         <v>Other Asset</v>
@@ -561,13 +561,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Due from Aistra Labs Inc (US)</v>
+        <v>Investment - Unconstrained INC</v>
       </c>
       <c r="B12" t="str">
-        <v>1450</v>
+        <v>1402</v>
       </c>
       <c r="C12" t="str">
-        <v>Other Current Asset</v>
+        <v>Other Asset</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -575,10 +575,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Due from Aistra Labs UK Ltd</v>
+        <v>Due from Aistra Labs Inc (US)</v>
       </c>
       <c r="B13" t="str">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="C13" t="str">
         <v>Other Current Asset</v>
@@ -589,10 +589,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Due from Aistra Labs AI Software LLC (UAE)</v>
+        <v>Due from Aistra Labs UK Ltd</v>
       </c>
       <c r="B14" t="str">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="C14" t="str">
         <v>Other Current Asset</v>
@@ -603,10 +603,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Due from Unconstrained INC</v>
+        <v>Due from Aistra Labs AI Software LLC (UAE)</v>
       </c>
       <c r="B15" t="str">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="C15" t="str">
         <v>Other Current Asset</v>
@@ -617,10 +617,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Advance to Suppliers</v>
+        <v>Due from Unconstrained INC</v>
       </c>
       <c r="B16" t="str">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="C16" t="str">
         <v>Other Current Asset</v>
@@ -631,13 +631,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Computers and Equipment</v>
+        <v>Advance to Suppliers</v>
       </c>
       <c r="B17" t="str">
-        <v>1500</v>
+        <v>1455</v>
       </c>
       <c r="C17" t="str">
-        <v>Fixed Asset</v>
+        <v>Other Current Asset</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -645,10 +645,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Accumulated Depreciation - Computers and Equipment</v>
+        <v>Computers and Equipment (net)</v>
       </c>
       <c r="B18" t="str">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="C18" t="str">
         <v>Fixed Asset</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Furniture and Fixtures</v>
+        <v>Furniture and Fixtures (net)</v>
       </c>
       <c r="B19" t="str">
         <v>1520</v>
@@ -673,13 +673,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Accumulated Depreciation - Furniture and Fixtures</v>
+        <v>Deferred Tax Asset</v>
       </c>
       <c r="B20" t="str">
-        <v>1530</v>
+        <v>1600</v>
       </c>
       <c r="C20" t="str">
-        <v>Fixed Asset</v>
+        <v>Other Asset</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -687,13 +687,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Deferred Tax Asset</v>
+        <v>Accounts Payable</v>
       </c>
       <c r="B21" t="str">
-        <v>1600</v>
+        <v>2001</v>
       </c>
       <c r="C21" t="str">
-        <v>Other Asset</v>
+        <v>Accounts Payable</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -701,13 +701,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Accounts Payable</v>
+        <v>Accrued Expenses</v>
       </c>
       <c r="B22" t="str">
-        <v>2001</v>
+        <v>2100</v>
       </c>
       <c r="C22" t="str">
-        <v>Accounts Payable</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -715,10 +715,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Accrued Expenses</v>
+        <v>Income Tax Payable</v>
       </c>
       <c r="B23" t="str">
-        <v>2100</v>
+        <v>2150</v>
       </c>
       <c r="C23" t="str">
         <v>Other Current Liability</v>
@@ -729,10 +729,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Income Tax Payable</v>
+        <v>Provision for Leave Encashment</v>
       </c>
       <c r="B24" t="str">
-        <v>2150</v>
+        <v>2200</v>
       </c>
       <c r="C24" t="str">
         <v>Other Current Liability</v>
@@ -743,10 +743,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Provision for Leave Encashment</v>
+        <v>Provision for Gratuity</v>
       </c>
       <c r="B25" t="str">
-        <v>2200</v>
+        <v>2210</v>
       </c>
       <c r="C25" t="str">
         <v>Other Current Liability</v>
@@ -757,10 +757,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Provision for Gratuity</v>
+        <v>TDS Payable</v>
       </c>
       <c r="B26" t="str">
-        <v>2210</v>
+        <v>2300</v>
       </c>
       <c r="C26" t="str">
         <v>Other Current Liability</v>
@@ -771,13 +771,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>TDS Payable</v>
+        <v>Equity Share Capital</v>
       </c>
       <c r="B27" t="str">
-        <v>2300</v>
+        <v>3001</v>
       </c>
       <c r="C27" t="str">
-        <v>Other Current Liability</v>
+        <v>Equity</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -785,10 +785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Equity Share Capital</v>
+        <v>Securities Premium</v>
       </c>
       <c r="B28" t="str">
-        <v>3001</v>
+        <v>3100</v>
       </c>
       <c r="C28" t="str">
         <v>Equity</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Securities Premium</v>
+        <v>Retained Earnings</v>
       </c>
       <c r="B29" t="str">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="C29" t="str">
         <v>Equity</v>
@@ -813,13 +813,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Retained Earnings</v>
+        <v>Sales</v>
       </c>
       <c r="B30" t="str">
-        <v>3200</v>
+        <v>4000</v>
       </c>
       <c r="C30" t="str">
-        <v>Equity</v>
+        <v>Income</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -827,10 +827,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Consulting Revenue</v>
+        <v>IC Revenue - US</v>
       </c>
       <c r="B31" t="str">
-        <v>4001</v>
+        <v>4100</v>
       </c>
       <c r="C31" t="str">
         <v>Income</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>IC Revenue - US</v>
+        <v>IC Revenue - UK</v>
       </c>
       <c r="B32" t="str">
-        <v>4100</v>
+        <v>4101</v>
       </c>
       <c r="C32" t="str">
         <v>Income</v>
@@ -855,10 +855,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>IC Revenue - UK</v>
+        <v>IC Revenue - UAE</v>
       </c>
       <c r="B33" t="str">
-        <v>4101</v>
+        <v>4102</v>
       </c>
       <c r="C33" t="str">
         <v>Income</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>IC Revenue - UAE</v>
+        <v>IC Revenue - Unconstrained</v>
       </c>
       <c r="B34" t="str">
-        <v>4102</v>
+        <v>4103</v>
       </c>
       <c r="C34" t="str">
         <v>Income</v>
@@ -883,13 +883,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>IC Revenue - Unconstrained</v>
+        <v>Interest Income</v>
       </c>
       <c r="B35" t="str">
-        <v>4103</v>
+        <v>4500</v>
       </c>
       <c r="C35" t="str">
-        <v>Income</v>
+        <v>Other Income</v>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -897,13 +897,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Interest Income</v>
+        <v>Cost of Services</v>
       </c>
       <c r="B36" t="str">
-        <v>4500</v>
+        <v>5001</v>
       </c>
       <c r="C36" t="str">
-        <v>Other Income</v>
+        <v>Cost Of Goods Sold</v>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -911,13 +911,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Cost of Services</v>
+        <v>Salaries and Wages</v>
       </c>
       <c r="B37" t="str">
-        <v>5001</v>
+        <v>6001</v>
       </c>
       <c r="C37" t="str">
-        <v>Cost Of Goods Sold</v>
+        <v>Expense</v>
       </c>
       <c r="D37" t="str">
         <v/>
@@ -925,10 +925,10 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Salaries and Wages</v>
+        <v>Contribution to Provident Fund</v>
       </c>
       <c r="B38" t="str">
-        <v>6001</v>
+        <v>6010</v>
       </c>
       <c r="C38" t="str">
         <v>Expense</v>
@@ -939,10 +939,10 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Contribution to Provident Fund</v>
+        <v>Gratuity Expense</v>
       </c>
       <c r="B39" t="str">
-        <v>6010</v>
+        <v>6020</v>
       </c>
       <c r="C39" t="str">
         <v>Expense</v>
